--- a/tools/xlsform_samples/WCHS.xlsx
+++ b/tools/xlsform_samples/WCHS.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>total (mean_coded) - Mean of all 10 items (1–100). Higher scores indicate stronger belief that words can cause lasting psychological harm.</t>
+          <t>total (mean_coded) - Mean of all 10 items (1-100). Higher scores indicate stronger belief that words can cause lasting psychological harm.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>

--- a/tools/xlsform_samples/WCHS.xlsx
+++ b/tools/xlsform_samples/WCHS.xlsx
@@ -442,11 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -890,84 +890,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WCHS_scoring</t>
+          <t>WCHS_total</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>total (mean_coded) - Mean of all 10 items (1-100). Higher scores indicate stronger belief that words can cause lasting psychological harm.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>(${wchs1} + ${wchs2} + ${wchs3} + ${wchs4} + ${wchs5} + ${wchs6} + ${wchs7} + ${wchs8} + ${wchs9} + ${wchs10}) div 10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>WCHS_total</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>total (mean_coded) - Mean of all 10 items (1-100). Higher scores indicate stronger belief that words can cause lasting psychological harm.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>(${wchs1} + ${wchs2} + ${wchs3} + ${wchs4} + ${wchs5} + ${wchs6} + ${wchs7} + ${wchs8} + ${wchs9} + ${wchs10}) div 10</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>WCHS_scoring</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/WCHS.xlsx
+++ b/tools/xlsform_samples/WCHS.xlsx
@@ -1011,7 +1011,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
